--- a/static/Upload/IEM marks.xlsx
+++ b/static/Upload/IEM marks.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">A3</t>
   </si>
   <si>
-    <t xml:space="preserve">Mid Term</t>
+    <t xml:space="preserve">Mid Term (25)</t>
   </si>
   <si>
     <t xml:space="preserve">23/ME/227</t>

--- a/static/Upload/IEM marks.xlsx
+++ b/static/Upload/IEM marks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="109">
   <si>
     <t xml:space="preserve">Sr No</t>
   </si>
@@ -61,25 +61,25 @@
     <t xml:space="preserve">SAGAR  RAWAT</t>
   </si>
   <si>
+    <t xml:space="preserve">23/ME/234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAKSHAM  JAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/ME/238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANCHIT  DUGGAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/ME/239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANJAY  SONI</t>
+  </si>
+  <si>
     <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/ME/234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAKSHAM  JAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/ME/238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANCHIT  DUGGAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/ME/239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANJAY  SONI</t>
   </si>
   <si>
     <t xml:space="preserve">23/ME/247</t>
@@ -531,10 +531,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>25</v>
@@ -545,10 +545,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>3</v>
@@ -565,10 +565,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>5</v>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>19</v>
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>12</v>
@@ -751,7 +751,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>5</v>
@@ -934,7 +934,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>22</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>21</v>
@@ -974,7 +974,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>22</v>
@@ -1034,7 +1034,7 @@
         <v>5</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>25</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>23</v>
@@ -1074,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>23</v>
@@ -1094,7 +1094,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>21</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>22</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>15</v>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>23</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>21</v>
@@ -1314,7 +1314,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>22</v>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>24</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>22</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>10</v>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>19</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>23</v>

--- a/static/Upload/IEM marks.xlsx
+++ b/static/Upload/IEM marks.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,8 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Student Data" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Student Data" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Student Data'!$F$1:$F$52</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -422,12 +425,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -440,1073 +451,1355 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1018" min="4" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1017" min="4" style="2" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="E2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="n">
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1" t="n">
+      <c r="D4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1" t="n">
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="n">
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="1" t="n">
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1" t="n">
+      <c r="D8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1" t="n">
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1" t="n">
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="1" t="n">
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="1" t="n">
+      <c r="D12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="1" t="n">
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="1" t="n">
+      <c r="D14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="1" t="n">
+      <c r="D15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="1" t="n">
+      <c r="D16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="1" t="n">
+      <c r="E17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1" t="n">
+      <c r="D18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" s="1" t="n">
+      <c r="D19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1" t="n">
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1" t="n">
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1" t="n">
+      <c r="D22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" s="1" t="n">
+      <c r="D23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="F23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="1" t="n">
+      <c r="D24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="1" t="n">
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="1" t="n">
+      <c r="E26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="1" t="n">
+      <c r="D27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="1" t="n">
+      <c r="D28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="1" t="n">
+      <c r="D29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="1" t="n">
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="1" t="n">
+      <c r="D31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="1" t="n">
+      <c r="D32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="1" t="n">
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="1" t="n">
+      <c r="D34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" s="1" t="n">
+      <c r="D35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="F35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G36" s="1" t="n">
+      <c r="D36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="1" t="n">
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" s="1" t="n">
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" s="1" t="n">
+      <c r="D39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" s="1" t="n">
+      <c r="D40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="1" t="n">
+      <c r="D41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" s="1" t="n">
+      <c r="D42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" s="1" t="n">
+      <c r="E43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="1" t="n">
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="1" t="n">
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="1" t="n">
+      <c r="D46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G46" s="1" t="n">
+      <c r="F46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" s="1" t="n">
+      <c r="E47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="1" t="n">
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="1" t="n">
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G50" s="1" t="n">
+      <c r="D50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="1" t="n">
+      <c r="D51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" s="1" t="n">
+      <c r="D52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="n">
         <v>23</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="F1:F52"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>